--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106390</v>
+        <v>106396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106398</v>
+        <v>106399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106399</v>
+        <v>106405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106405</v>
+        <v>106409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106409</v>
+        <v>106411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106411</v>
+        <v>106413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106413</v>
+        <v>106426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106426</v>
+        <v>106428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106428</v>
+        <v>106432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106432</v>
+        <v>106451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106451</v>
+        <v>106452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106452</v>
+        <v>106457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106457</v>
+        <v>106460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106460</v>
+        <v>106466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106466</v>
+        <v>106467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106467</v>
+        <v>106479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106479</v>
+        <v>106480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106480</v>
+        <v>106483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106483</v>
+        <v>106485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2025 artfynd.xlsx
+++ b/artfynd/A 60614-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954212</v>
       </c>
       <c r="B2" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136954213</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136954215</v>
       </c>
       <c r="B4" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136954216</v>
       </c>
       <c r="B5" t="n">
-        <v>106485</v>
+        <v>106489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
